--- a/docs/StructureDefinition-MedicationDispensePartialMedicationDispense.xlsx
+++ b/docs/StructureDefinition-MedicationDispensePartialMedicationDispense.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.9.0</t>
+    <t>0.10.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T07:51:53+00:00</t>
+    <t>2023-12-21T16:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispensePartialMedicationDispense.xlsx
+++ b/docs/StructureDefinition-MedicationDispensePartialMedicationDispense.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.10.0</t>
+    <t>0.11.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-21T16:22:28+00:00</t>
+    <t>2023-12-28T09:08:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispensePartialMedicationDispense.xlsx
+++ b/docs/StructureDefinition-MedicationDispensePartialMedicationDispense.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.11.0</t>
+    <t>0.12.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-28T09:08:39+00:00</t>
+    <t>2023-12-29T17:54:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-MedicationDispensePartialMedicationDispense.xlsx
+++ b/docs/StructureDefinition-MedicationDispensePartialMedicationDispense.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.12.0</t>
+    <t>0.13.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-12-29T17:54:36+00:00</t>
+    <t>2024-01-03T19:41:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This StructureDefinition contains the maps for VistA PRESCRIPTION (file 52) to FHIR MedicationDispense</t>
+    <t>This StructureDefinition contains the maps for VistA file PRESCRIPTION (#52) to MedicationDispense</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -543,7 +543,7 @@
   </si>
   <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-inv-39:1577: fixed value = completed if PRESCRIPTION - PARTIAL DATE &gt; PARTIAL DATE - RELEASED DATE/TIME (#52-60 &gt; 52.2-8) case not null {null}inv-40:1578: fixed value = in-progress if PRESCRIPTION - PARTIAL DATE &gt; PARTIAL DATE - RELEASED DATE/TIME (#52-60 &gt; 52.2-8) case null {null}</t>
+inv-39:1577: fixed value = completed when PRESCRIPTION - PARTIAL DATE &gt; PARTIAL DATE - RELEASED DATE/TIME (#52-60 &gt; 52.2-8) case not null {null}inv-40:1578: fixed value = in-progress when PRESCRIPTION - PARTIAL DATE &gt; PARTIAL DATE - RELEASED DATE/TIME (#52-60 &gt; 52.2-8) case null {null}</t>
   </si>
   <si>
     <t>Event.status</t>
@@ -558,7 +558,7 @@
     <t>CombinedMedicationDispense.SupplyEvent.statusCode</t>
   </si>
   <si>
-    <t>1578: fixed value = in-progress if PRESCRIPTION - PARTIAL DATE &gt; PARTIAL DATE - RELEASED DATE/TIME (#52-60 &gt; 52.2-8) case null</t>
+    <t>1578: fixed value = in-progress when PRESCRIPTION - PARTIAL DATE &gt; PARTIAL DATE - RELEASED DATE/TIME (#52-60 &gt; 52.2-8) case null</t>
   </si>
   <si>
     <t>MedicationDispense.statusReason[x]</t>
